--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raba383b58c73478e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc6a0d51e64ef4ccd"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc6a0d51e64ef4ccd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4e1336e11ca64781"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4e1336e11ca64781"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4eb386dcea3b407a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4eb386dcea3b407a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf5f22bbaf8a44e50"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf5f22bbaf8a44e50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2c5d228512b24c57"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2c5d228512b24c57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6ac0c42ce90c451b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6ac0c42ce90c451b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re62c70e1c05648b5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re62c70e1c05648b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7c7b669a52a14b53"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7c7b669a52a14b53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3bd8b44cfa174a9b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3bd8b44cfa174a9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7f39955f290e4150"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7f39955f290e4150"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R42c269d0ede04dc2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R42c269d0ede04dc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R60e57127ce484a1d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R60e57127ce484a1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R64685af4666f47fa"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R64685af4666f47fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4455b6bf8c8a4d70"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4455b6bf8c8a4d70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra71e0c89204b4693"/>
   </x:sheets>
 </x:workbook>
 </file>
